--- a/data/trans_dic/P19C10_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C10_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,46</t>
+          <t>0,36; 3,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,44</t>
+          <t>0,16; 1,49</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,78</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,02</t>
+          <t>0,03; 1,2</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,49</t>
+          <t>0,26; 2,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,52</t>
+          <t>0,24; 1,41</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,28</t>
+          <t>0,28; 1,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,77</t>
+          <t>0,17; 0,85</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,16</t>
+          <t>0,11; 1,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,54</t>
+          <t>0,06; 0,58</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,15</t>
+          <t>0,09; 1,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,78</t>
+          <t>0,08; 0,67</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,86</t>
+          <t>0,46; 1,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,34</t>
+          <t>0,35; 1,29</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,57</t>
+          <t>0,15; 0,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,82</t>
+          <t>0,38; 0,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,62</t>
+          <t>0,31; 0,6</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4655</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1128; 10515</t>
+          <t>1088; 9992</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1125; 9880</t>
+          <t>1118; 10252</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 11200</t>
+          <t>0; 7632</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6057</t>
+          <t>0; 5598</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>163; 9199</t>
+          <t>273; 10858</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1326; 13034</t>
+          <t>1343; 12283</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5065</t>
+          <t>0; 4501</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2750; 16054</t>
+          <t>2578; 14911</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7902</t>
+          <t>0; 9076</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1707; 8939</t>
+          <t>1973; 9030</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2600; 12094</t>
+          <t>2669; 13301</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1625</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>641; 6178</t>
+          <t>568; 5428</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>596; 5788</t>
+          <t>693; 6311</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2402</t>
+          <t>0; 2440</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>543; 6891</t>
+          <t>542; 7625</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1136; 7457</t>
+          <t>731; 6434</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3718</t>
+          <t>0; 3115</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1695; 7604</t>
+          <t>1862; 7831</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2308; 9191</t>
+          <t>2398; 8832</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4182; 18953</t>
+          <t>5032; 19801</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13197; 29381</t>
+          <t>13498; 28889</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>20987; 42989</t>
+          <t>21345; 41908</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C10_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C10_2023-Edad-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,29</t>
+          <t>0,36; 3,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,49</t>
+          <t>0,17; 1,45</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,2</t>
+          <t>0,12; 1,39</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,34</t>
+          <t>0,22; 2,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,41</t>
+          <t>0,18; 1,14</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,29</t>
+          <t>0,36; 1,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,85</t>
+          <t>0,3; 1,05</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,02</t>
+          <t>0,1; 1,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,58</t>
+          <t>0,06; 0,56</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,27</t>
+          <t>0,28; 1,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,67</t>
+          <t>0,16; 0,92</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,92</t>
+          <t>0,44; 1,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,29</t>
+          <t>0,37; 1,36</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,59</t>
+          <t>0,15; 0,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,81</t>
+          <t>0,43; 0,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,6</t>
+          <t>0,35; 0,66</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3877</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1088; 9992</t>
+          <t>1220; 10600</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1118; 10252</t>
+          <t>1192; 10465</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>3989</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7632</t>
+          <t>0; 8524</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5598</t>
+          <t>0; 6470</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>273; 10858</t>
+          <t>1070; 12944</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>6725</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1343; 12283</t>
+          <t>1323; 13003</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4501</t>
+          <t>0; 5340</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2578; 14911</t>
+          <t>2229; 13812</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>7676</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9076</t>
+          <t>0; 7898</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1973; 9030</t>
+          <t>2591; 10022</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2669; 13301</t>
+          <t>4137; 14632</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2635</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>568; 5428</t>
+          <t>606; 6261</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>693; 6311</t>
+          <t>718; 6699</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3637</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2440</t>
+          <t>0; 3017</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>542; 7625</t>
+          <t>1209; 6808</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>731; 6434</t>
+          <t>1286; 7623</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>955</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5200</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3115</t>
+          <t>0; 4708</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1862; 7831</t>
+          <t>1963; 8340</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2398; 8832</t>
+          <t>2758; 10205</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>22984</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>33739</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5032; 19801</t>
+          <t>5019; 20541</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13498; 28889</t>
+          <t>15731; 33037</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21345; 41908</t>
+          <t>24385; 46626</t>
         </is>
       </c>
     </row>
